--- a/tests/reports/frontend_test_report.xlsx
+++ b/tests/reports/frontend_test_report.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:41</t>
+          <t>2026-06-18 14:18:41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="K2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="K3" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="K4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="K11" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:36</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K25" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="K29" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K30" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="K31" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="K32" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="K33" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="K34" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="K35" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="K36" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="K38" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="K41" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="K42" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="K43" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="K44" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:36</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="K45" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="K46" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K47" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="K48" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="K49" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K50" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K51" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="K52" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="K53" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K54" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K55" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="K56" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="K57" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="K58" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="K59" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="K60" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="K61" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="K62" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="K63" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="K64" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="K65" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K66" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="K67" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="K68" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="K69" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="K70" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="K71" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="K72" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="K73" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:37</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="K74" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="K75" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="K76" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="K77" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="K78" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="K79" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="K80" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="K81" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="K82" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="K83" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="K84" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="K85" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="K86" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="K87" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="K88" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="K89" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="K90" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="K91" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="K92" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="K93" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:37</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="K94" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="K95" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K96" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="K97" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K98" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="K99" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="K100" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="K101" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="K102" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="K103" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="K104" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="K105" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="K106" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K107" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="K108" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="K109" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="K110" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="K111" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="K112" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="K113" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K114" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K115" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="K116" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="K117" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="K118" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="K119" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="K120" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="K121" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="K122" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:38</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="K123" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="K124" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="K125" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="K126" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="K127" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="K128" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="K129" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="K130" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K131" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="K132" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="K133" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="K134" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="K135" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="K136" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="K137" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="K138" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K139" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="K140" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:38</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K141" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="K142" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="K143" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="K144" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="K145" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="K146" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="K147" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="K148" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="K149" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="K150" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="K151" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="K152" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="K153" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="K154" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="K155" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="K156" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="K157" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="K158" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="K159" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="K160" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="K161" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="K162" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="K163" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="K164" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="K165" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="K166" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="K167" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="K168" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="K169" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K170" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="K171" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="K172" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="K173" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="K174" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="K175" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="K176" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="K177" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K178" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="K179" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="K180" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="K181" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="K182" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="K183" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="K184" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="K185" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="K186" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="K187" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="K188" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="K189" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:39</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="K190" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="K191" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K192" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="K193" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="K194" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="K195" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="K196" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="K197" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="K198" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="K199" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="K200" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="K201" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:04:40</t>
+          <t>2026-06-18 14:18:40</t>
         </is>
       </c>
     </row>

--- a/tests/reports/frontend_test_report.xlsx
+++ b/tests/reports/frontend_test_report.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:41</t>
+          <t>2026-06-18 19:57:42</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="K2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="K3" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="K4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="K11" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:36</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K25" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="K29" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K30" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="K31" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="K32" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="K33" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="K34" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="K35" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="K36" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="K38" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="K41" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="K42" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="K43" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="K44" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:37</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="K45" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="K46" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K47" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="K48" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="K49" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K50" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K51" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="K52" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="K53" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K54" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K55" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="K56" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="K57" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="K58" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="K59" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="K60" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="K61" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="K62" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="K63" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="K64" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="K65" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K66" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="K67" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="K68" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="K69" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="K70" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="K71" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="K72" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="K73" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:37</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="K74" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="K75" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="K76" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="K77" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="K78" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="K79" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="K80" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="K81" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="K82" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="K83" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="K84" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="K85" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="K86" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="K87" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="K88" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="K89" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="K90" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="K91" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="K92" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:38</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="K93" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="K94" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="K95" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K96" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="K97" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K98" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="K99" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="K100" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="K101" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="K102" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="K103" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="K104" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="K105" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="K106" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K107" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="K108" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="K109" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="K110" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="K111" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="K112" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="K113" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K114" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K115" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="K116" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="K117" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="K118" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="K119" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="K120" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="K121" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="K122" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:38</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="K123" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="K124" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="K125" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="K126" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="K127" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="K128" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="K129" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="K130" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K131" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="K132" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="K133" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="K134" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="K135" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="K136" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="K137" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="K138" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K139" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="K140" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K141" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:39</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="K142" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="K143" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="K144" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="K145" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="K146" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="K147" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="K148" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="K149" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="K150" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="K151" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="K152" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="K153" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="K154" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="K155" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="K156" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="K157" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="K158" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="K159" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="K160" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="K161" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="K162" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="K163" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="K164" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="K165" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="K166" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="K167" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="K168" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="K169" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K170" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="K171" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:39</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="K172" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="K173" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="K174" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="K175" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="K176" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="K177" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K178" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="K179" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="K180" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="K181" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="K182" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="K183" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="K184" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="K185" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="K186" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="K187" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="K188" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="K189" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="K190" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:40</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="K191" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K192" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="K193" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="K194" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="K195" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="K196" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="K197" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="K198" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="K199" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="K200" s="18" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="K201" s="21" t="inlineStr">
         <is>
-          <t>2026-06-18 14:18:40</t>
+          <t>2026-06-18 19:57:41</t>
         </is>
       </c>
     </row>
